--- a/etf_holdings/2026-10-30_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00990A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:36</t>
+          <t>2026-10-30 23:08:50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,27 +509,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.41%2415</t>
+          <t>-1.86%2370</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.86%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2415</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.88%406,000</t>
+          <t>2.95%406,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.95%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -537,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:38</t>
+          <t>2026-10-30 23:08:51</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,27 +572,27 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-5.45%1040</t>
+          <t>-4.9%989</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.45%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>989</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.15%667,000</t>
+          <t>2.09%667,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -600,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:38</t>
+          <t>2026-10-30 23:08:51</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -630,40 +630,40 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>6098RECRUIT HOLDINGS CO LTD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.49%4045</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-4.49%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.05%165,000</t>
+          <t>2.04%174,100</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>165000</v>
+        <v>174100</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:38</t>
+          <t>2026-10-30 23:08:51</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,27 +698,27 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.3%5010</t>
+          <t>-6.69%4675</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-6.69%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5010</t>
+          <t>4675</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.97%134,000</t>
+          <t>2.02%134,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:38</t>
+          <t>2026-10-30 23:08:51</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -756,40 +756,40 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>6098RECRUIT HOLDINGS CO LTD</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.21%3915</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.97%174,100</t>
+          <t>2.01%165,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.01%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>174100</v>
+        <v>165000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:38</t>
+          <t>2026-10-30 23:08:51</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -819,40 +819,40 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-4.52%1480</t>
+          <t>-0.32%3095</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.52%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.91%420,000</t>
+          <t>1.48%158,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>420000</v>
+        <v>158000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:38</t>
+          <t>2026-10-30 23:08:51</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -882,40 +882,40 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-3.42%3105</t>
+          <t>-4.8%1190</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-3.42%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>1190</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.49%158,000</t>
+          <t>1.31%348,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>158000</v>
+        <v>348000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:39</t>
+          <t>2026-10-30 23:08:51</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -941,44 +941,44 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-3.85%1250</t>
+          <t>-8.52%1020</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-3.85%</t>
+          <t>-8.52%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.33%348,000</t>
+          <t>1.24%368,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>348000</v>
+        <v>368000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:39</t>
+          <t>2026-10-30 23:08:52</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1008,40 +1008,40 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.91%1115</t>
+          <t>-0.07%7635</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.91%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>7635</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.28%368,000</t>
+          <t>1.01%44,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.01%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>368000</v>
+        <v>44000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 00:10:39</t>
+          <t>2026-10-30 23:08:52</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,106 +1071,43 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.49%7640</t>
+          <t>-9.8%1335</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-6.49%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.05%44,000</t>
+          <t>0.78%176,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>44000</v>
+        <v>176000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
-        <is>
-          <t>登入查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-10-30 00:10:39</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2345智邦</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>-3.31%1755</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>-3.31%</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>1755</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1.03%193,000</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1.03%</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>193000</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-0.03%</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-10-30_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:50</t>
+          <t>2026-10-30 23:20:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:51</t>
+          <t>2026-10-30 23:20:34</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:51</t>
+          <t>2026-10-30 23:20:34</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:51</t>
+          <t>2026-10-30 23:20:34</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:51</t>
+          <t>2026-10-30 23:20:34</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:51</t>
+          <t>2026-10-30 23:20:34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:51</t>
+          <t>2026-10-30 23:20:34</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:51</t>
+          <t>2026-10-30 23:20:34</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:52</t>
+          <t>2026-10-30 23:20:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:08:52</t>
+          <t>2026-10-30 23:20:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">

--- a/etf_holdings/2026-10-30_00990A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-30_00990A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:33</t>
+          <t>2026-10-30 23:56:46</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:34</t>
+          <t>2026-10-30 23:56:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:34</t>
+          <t>2026-10-30 23:56:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:34</t>
+          <t>2026-10-30 23:56:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:34</t>
+          <t>2026-10-30 23:56:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:34</t>
+          <t>2026-10-30 23:56:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:34</t>
+          <t>2026-10-30 23:56:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:34</t>
+          <t>2026-10-30 23:56:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:35</t>
+          <t>2026-10-30 23:56:49</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-30 23:20:35</t>
+          <t>2026-10-30 23:56:49</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
